--- a/data/trans_dic/P44A$endoscopia-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,12; 76,58</t>
+          <t>27,01; 77,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,04; 61,41</t>
+          <t>23,93; 61,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,94; 52,68</t>
+          <t>35,18; 53,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,32; 87,35</t>
+          <t>40,93; 87,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,67; 72,92</t>
+          <t>31,48; 73,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,16; 47,68</t>
+          <t>34,04; 47,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,98; 74,88</t>
+          <t>39,84; 76,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,11; 61,05</t>
+          <t>33,04; 60,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,85; 48,37</t>
+          <t>36,32; 47,38</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,41; 83,39</t>
+          <t>40,32; 80,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,09; 73,36</t>
+          <t>44,21; 73,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,45; 94,56</t>
+          <t>41,23; 94,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50,98; 82,68</t>
+          <t>47,96; 81,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,4; 67,85</t>
+          <t>31,14; 68,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,54; 44,99</t>
+          <t>33,42; 45,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,18; 76,79</t>
+          <t>52,95; 77,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,16; 65,72</t>
+          <t>42,21; 66,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,23; 90,45</t>
+          <t>40,47; 88,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,06; 87,52</t>
+          <t>43,75; 86,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,46; 77,15</t>
+          <t>39,68; 75,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,58; 48,55</t>
+          <t>31,6; 48,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,55; 80,14</t>
+          <t>41,66; 82,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,58; 77,41</t>
+          <t>31,87; 76,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,54; 43,46</t>
+          <t>27,45; 44,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,64; 77,41</t>
+          <t>49,08; 77,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,18; 70,68</t>
+          <t>43,17; 70,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,23; 43,82</t>
+          <t>32,44; 44,97</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,62; 76,06</t>
+          <t>42,48; 74,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,93; 60,24</t>
+          <t>34,94; 61,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,04; 48,77</t>
+          <t>35,02; 47,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,21; 71,96</t>
+          <t>32,47; 71,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,05; 80,06</t>
+          <t>47,93; 81,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 39,07</t>
+          <t>27,96; 38,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,86; 68,9</t>
+          <t>43,69; 68,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,54; 65,5</t>
+          <t>43,73; 65,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,4; 41,68</t>
+          <t>33,7; 41,73</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,6; 71,36</t>
+          <t>52,35; 71,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,01; 59,97</t>
+          <t>43,79; 60,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,3; 83,32</t>
+          <t>41,8; 82,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,77; 71,17</t>
+          <t>51,64; 71,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,85; 65,62</t>
+          <t>45,02; 65,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,06; 39,47</t>
+          <t>33,29; 39,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,6; 69,23</t>
+          <t>54,51; 68,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,22; 59,71</t>
+          <t>47,59; 59,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,95; 72,6</t>
+          <t>38,93; 74,85</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3971; 11641</t>
+          <t>4106; 11855</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7427; 18970</t>
+          <t>7393; 18947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32103; 48405</t>
+          <t>32324; 48801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6129; 13277</t>
+          <t>6221; 13250</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8606; 18641</t>
+          <t>8046; 18702</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33306; 46489</t>
+          <t>33188; 46255</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12761; 22764</t>
+          <t>12112; 23213</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18689; 34466</t>
+          <t>18653; 34258</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69795; 91600</t>
+          <t>68782; 89735</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10659; 21999</t>
+          <t>10637; 21295</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17022; 28982</t>
+          <t>17465; 29173</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160403; 365945</t>
+          <t>159533; 364084</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18541; 30070</t>
+          <t>17443; 29817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10237; 22848</t>
+          <t>10486; 23152</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41389; 57222</t>
+          <t>42507; 58241</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32742; 48188</t>
+          <t>33226; 48902</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30851; 48096</t>
+          <t>30889; 48798</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>206835; 465082</t>
+          <t>208066; 457506</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12139; 23067</t>
+          <t>11531; 22837</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12458; 23754</t>
+          <t>12217; 23262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33685; 51777</t>
+          <t>33704; 52191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10449; 21173</t>
+          <t>11005; 21677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5803; 15716</t>
+          <t>6471; 15605</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19916; 31425</t>
+          <t>19851; 32231</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25672; 40854</t>
+          <t>25902; 40865</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22060; 36110</t>
+          <t>22057; 36240</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55881; 78412</t>
+          <t>58053; 80487</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18073; 31513</t>
+          <t>17600; 30975</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20435; 35242</t>
+          <t>20443; 36255</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68903; 93244</t>
+          <t>66950; 90642</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9328; 20840</t>
+          <t>9404; 20679</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16850; 29293</t>
+          <t>17534; 29856</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50894; 70757</t>
+          <t>50636; 69606</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30874; 48500</t>
+          <t>30753; 48550</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42355; 62285</t>
+          <t>41582; 62377</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124362; 155195</t>
+          <t>125489; 155358</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56432; 78039</t>
+          <t>57249; 77847</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70282; 95764</t>
+          <t>69928; 95964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>320782; 647154</t>
+          <t>324645; 638546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55368; 76114</t>
+          <t>55232; 76516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53248; 76196</t>
+          <t>52283; 76630</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>158068; 188697</t>
+          <t>159143; 189444</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>118116; 149759</t>
+          <t>117916; 147087</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>130232; 164680</t>
+          <t>131253; 165398</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>488756; 910962</t>
+          <t>488561; 939193</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$endoscopia-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,01; 77,99</t>
+          <t>24,65; 73,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,93; 61,34</t>
+          <t>23,1; 60,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,18; 53,11</t>
+          <t>37,76; 54,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,93; 87,17</t>
+          <t>40,29; 87,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,48; 73,16</t>
+          <t>31,0; 72,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,04; 47,44</t>
+          <t>34,85; 47,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,84; 76,36</t>
+          <t>43,14; 76,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,04; 60,68</t>
+          <t>32,41; 61,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,32; 47,38</t>
+          <t>37,76; 48,75</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,32; 80,72</t>
+          <t>39,66; 80,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,21; 73,85</t>
+          <t>42,71; 73,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,23; 94,08</t>
+          <t>39,3; 53,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,96; 81,99</t>
+          <t>48,99; 82,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,14; 68,75</t>
+          <t>30,86; 68,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,42; 45,79</t>
+          <t>33,44; 45,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,95; 77,93</t>
+          <t>52,05; 78,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,21; 66,68</t>
+          <t>41,91; 66,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,47; 88,98</t>
+          <t>38,0; 47,71</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,75; 86,65</t>
+          <t>43,18; 84,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,68; 75,55</t>
+          <t>39,94; 76,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,6; 48,93</t>
+          <t>33,6; 50,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,66; 82,05</t>
+          <t>39,74; 78,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,87; 76,87</t>
+          <t>28,11; 77,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,45; 44,58</t>
+          <t>27,43; 43,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,08; 77,43</t>
+          <t>49,59; 78,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,17; 70,93</t>
+          <t>43,01; 71,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,44; 44,97</t>
+          <t>33,7; 45,36</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,48; 74,76</t>
+          <t>41,25; 74,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,94; 61,97</t>
+          <t>35,23; 62,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,02; 47,41</t>
+          <t>35,62; 47,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,47; 71,4</t>
+          <t>33,7; 72,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,93; 81,6</t>
+          <t>45,14; 79,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,96; 38,43</t>
+          <t>27,09; 37,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,69; 68,97</t>
+          <t>42,94; 68,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,73; 65,6</t>
+          <t>44,19; 65,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,7; 41,73</t>
+          <t>32,84; 40,47</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,35; 71,18</t>
+          <t>50,73; 71,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,79; 60,1</t>
+          <t>43,78; 59,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,8; 82,21</t>
+          <t>39,24; 47,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,64; 71,54</t>
+          <t>51,54; 71,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,02; 65,99</t>
+          <t>45,67; 65,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,29; 39,62</t>
+          <t>33,4; 39,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,51; 68,0</t>
+          <t>54,16; 68,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,59; 59,97</t>
+          <t>47,5; 60,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,93; 74,85</t>
+          <t>37,66; 42,33</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39500</t>
+          <t>43306</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79734</t>
+          <t>89189</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4106; 11855</t>
+          <t>3747; 11242</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7393; 18947</t>
+          <t>7136; 18620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32324; 48801</t>
+          <t>38072; 55392</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6221; 13250</t>
+          <t>6125; 13227</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8046; 18702</t>
+          <t>7924; 18569</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33188; 46255</t>
+          <t>36900; 50757</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12112; 23213</t>
+          <t>13116; 23368</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18653; 34258</t>
+          <t>18296; 34470</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>68782; 89735</t>
+          <t>78056; 100778</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49519</t>
+          <t>54903</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>356911</t>
+          <t>125259</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10637; 21295</t>
+          <t>10462; 21165</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17465; 29173</t>
+          <t>16874; 29047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159533; 364084</t>
+          <t>60510; 81930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17443; 29817</t>
+          <t>17816; 29969</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10486; 23152</t>
+          <t>10393; 22988</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42507; 58241</t>
+          <t>46923; 64168</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33226; 48902</t>
+          <t>32660; 49164</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30889; 48798</t>
+          <t>30669; 48723</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>208066; 457506</t>
+          <t>111846; 140405</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42661</t>
+          <t>49451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25713</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68374</t>
+          <t>79615</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11531; 22837</t>
+          <t>11380; 22302</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12217; 23262</t>
+          <t>12299; 23539</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33704; 52191</t>
+          <t>39667; 59528</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11005; 21677</t>
+          <t>10499; 20824</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6471; 15605</t>
+          <t>5706; 15638</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19851; 32231</t>
+          <t>23339; 36653</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25902; 40865</t>
+          <t>26171; 41373</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22057; 36240</t>
+          <t>21974; 36678</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58053; 80487</t>
+          <t>68464; 92153</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80142</t>
+          <t>81713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>63814</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>139713</t>
+          <t>145526</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17600; 30975</t>
+          <t>17091; 31062</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20443; 36255</t>
+          <t>20613; 36716</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66950; 90642</t>
+          <t>70530; 93541</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9404; 20679</t>
+          <t>9760; 20870</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17534; 29856</t>
+          <t>16514; 29208</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50636; 69606</t>
+          <t>53364; 74435</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30753; 48550</t>
+          <t>30229; 48394</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41582; 62377</t>
+          <t>42024; 62126</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125489; 155358</t>
+          <t>129689; 159850</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470429</t>
+          <t>247403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>644732</t>
+          <t>439588</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57249; 77847</t>
+          <t>55486; 78290</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69928; 95964</t>
+          <t>69918; 94738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>324645; 638546</t>
+          <t>224008; 268391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55232; 76516</t>
+          <t>55119; 76255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52283; 76630</t>
+          <t>53034; 75580</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>159143; 189444</t>
+          <t>176466; 209550</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>117916; 147087</t>
+          <t>117157; 147876</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131253; 165398</t>
+          <t>131008; 166096</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>488561; 939193</t>
+          <t>413953; 465238</t>
         </is>
       </c>
     </row>
